--- a/output/pdf_financials_xlsx/DLTA.xlsx
+++ b/output/pdf_financials_xlsx/DLTA.xlsx
@@ -2257,10 +2257,10 @@
         <v>0.772284</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.06776699999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.938809</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.992299</v>
@@ -2272,7 +2272,7 @@
         <v>5.651128</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.429983</v>
       </c>
     </row>
     <row r="35">
@@ -2337,10 +2337,10 @@
         <v>0.772284</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.06776699999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.938809</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.992299</v>
@@ -2352,7 +2352,7 @@
         <v>5.651128</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.429983</v>
       </c>
     </row>
     <row r="37">
@@ -2817,10 +2817,10 @@
         <v>0.224533</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.08305899999999999</v>
+        <v>0.015292</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.052781</v>
+        <v>0.113972</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.366733</v>
@@ -2832,7 +2832,7 @@
         <v>0.458792</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.75912</v>
+        <v>0.329137</v>
       </c>
     </row>
     <row r="49">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
